--- a/input/requirements/DeviceUse.xlsx
+++ b/input/requirements/DeviceUse.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichalCiszewski\Documents\Github\GBB-IG\input\requirements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GBB-IG\input\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3CC70A-F4FD-4030-AD9D-CC2A8DC81138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -4209,14 +4209,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4427,21 +4425,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
-    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4466,9 +4463,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
+    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>